--- a/automotive_forms/034_mechanic_activity_log--automotive_forms.xlsx
+++ b/automotive_forms/034_mechanic_activity_log--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>start time</t>
+          <t>Start Time H</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>end time</t>
+          <t>End Time H</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'toyota'}</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Toyota'}</t>
+          <t>Toyota</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'ford'}</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Ford'}</t>
+          <t>Ford</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'honda'}</t>
+          <t>honda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Honda'}</t>
+          <t>Honda</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'chevrolet'}</t>
+          <t>chevrolet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Chevrolet'}</t>
+          <t>Chevrolet</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'repair'}</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Repair'}</t>
+          <t>Repair</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'inspection'}</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Inspection'}</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Chatjimmy'}</t>
+          <t>Chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'automotive_forms'}</t>
+          <t>automotive_forms</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Automotive Forms'}</t>
+          <t>Automotive Forms</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
